--- a/annotated_data/mcmaster_reddit_part_3_A.xlsx
+++ b/annotated_data/mcmaster_reddit_part_3_A.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pgrew\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mcmasteru365-my.sharepoint.com/personal/guz38_mcmaster_ca/Documents/COMPSCI 4NL3/cs4nl-final-project/annotated_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6F097C2-E5D3-46D9-8318-412C180C34CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{D6F097C2-E5D3-46D9-8318-412C180C34CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C322D855-D0D9-4CCA-B52D-4C3E7EC7CBE8}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="16305" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4740" yWindow="3960" windowWidth="28800" windowHeight="15370" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="184">
   <si>
     <t>id</t>
   </si>
@@ -695,19 +695,10 @@
     <t xml:space="preserve"> M</t>
   </si>
   <si>
-    <t>m</t>
-  </si>
-  <si>
-    <t>f</t>
-  </si>
-  <si>
     <t>A</t>
   </si>
   <si>
     <t>U</t>
-  </si>
-  <si>
-    <t>,</t>
   </si>
   <si>
     <t>D</t>
@@ -975,12 +966,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C174"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="68" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -991,7 +982,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="120" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>517</v>
       </c>
@@ -1002,7 +993,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>518</v>
       </c>
@@ -1013,7 +1004,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>519</v>
       </c>
@@ -1024,7 +1015,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="120" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>520</v>
       </c>
@@ -1035,7 +1026,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>521</v>
       </c>
@@ -1046,7 +1037,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>522</v>
       </c>
@@ -1057,7 +1048,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>523</v>
       </c>
@@ -1068,7 +1059,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>524</v>
       </c>
@@ -1079,7 +1070,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="87" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>525</v>
       </c>
@@ -1090,7 +1081,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>526</v>
       </c>
@@ -1101,7 +1092,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>527</v>
       </c>
@@ -1112,7 +1103,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>528</v>
       </c>
@@ -1123,7 +1114,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="165" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>529</v>
       </c>
@@ -1134,7 +1125,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>530</v>
       </c>
@@ -1145,7 +1136,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>531</v>
       </c>
@@ -1156,7 +1147,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>532</v>
       </c>
@@ -1167,7 +1158,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="174" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>533</v>
       </c>
@@ -1178,7 +1169,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>534</v>
       </c>
@@ -1189,7 +1180,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>535</v>
       </c>
@@ -1200,7 +1191,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>536</v>
       </c>
@@ -1211,15 +1202,18 @@
         <v>180</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>537</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" ht="285" x14ac:dyDescent="0.25">
+      <c r="C22" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>538</v>
       </c>
@@ -1227,10 +1221,10 @@
         <v>24</v>
       </c>
       <c r="C23" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>539</v>
       </c>
@@ -1238,10 +1232,10 @@
         <v>25</v>
       </c>
       <c r="C24" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>540</v>
       </c>
@@ -1249,10 +1243,10 @@
         <v>26</v>
       </c>
       <c r="C25" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>541</v>
       </c>
@@ -1260,10 +1254,10 @@
         <v>27</v>
       </c>
       <c r="C26" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="409.5" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="391.5" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>542</v>
       </c>
@@ -1274,7 +1268,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>543</v>
       </c>
@@ -1285,7 +1279,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>544</v>
       </c>
@@ -1296,7 +1290,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>545</v>
       </c>
@@ -1307,7 +1301,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="105" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>546</v>
       </c>
@@ -1318,7 +1312,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>547</v>
       </c>
@@ -1329,7 +1323,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="135" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" ht="116" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>548</v>
       </c>
@@ -1337,10 +1331,10 @@
         <v>34</v>
       </c>
       <c r="C33" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>549</v>
       </c>
@@ -1351,7 +1345,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>550</v>
       </c>
@@ -1362,7 +1356,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>551</v>
       </c>
@@ -1373,7 +1367,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>552</v>
       </c>
@@ -1384,7 +1378,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="300" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" ht="290" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>553</v>
       </c>
@@ -1395,7 +1389,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>554</v>
       </c>
@@ -1403,10 +1397,10 @@
         <v>40</v>
       </c>
       <c r="C39" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>555</v>
       </c>
@@ -1417,7 +1411,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>556</v>
       </c>
@@ -1428,7 +1422,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>557</v>
       </c>
@@ -1439,7 +1433,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>558</v>
       </c>
@@ -1447,10 +1441,10 @@
         <v>44</v>
       </c>
       <c r="C43" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" ht="180" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="174" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>559</v>
       </c>
@@ -1461,7 +1455,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>560</v>
       </c>
@@ -1472,7 +1466,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="180" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>561</v>
       </c>
@@ -1483,7 +1477,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>562</v>
       </c>
@@ -1494,7 +1488,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>563</v>
       </c>
@@ -1505,7 +1499,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>564</v>
       </c>
@@ -1516,7 +1510,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>565</v>
       </c>
@@ -1527,7 +1521,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>566</v>
       </c>
@@ -1538,7 +1532,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>567</v>
       </c>
@@ -1549,7 +1543,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>568</v>
       </c>
@@ -1560,7 +1554,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>569</v>
       </c>
@@ -1568,7 +1562,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>570</v>
       </c>
@@ -1579,7 +1573,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>571</v>
       </c>
@@ -1590,7 +1584,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>572</v>
       </c>
@@ -1601,7 +1595,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="165" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>573</v>
       </c>
@@ -1612,7 +1606,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>574</v>
       </c>
@@ -1623,7 +1617,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>575</v>
       </c>
@@ -1634,7 +1628,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>576</v>
       </c>
@@ -1645,7 +1639,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>577</v>
       </c>
@@ -1656,7 +1650,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>578</v>
       </c>
@@ -1667,7 +1661,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>579</v>
       </c>
@@ -1678,7 +1672,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>580</v>
       </c>
@@ -1689,7 +1683,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="150" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>581</v>
       </c>
@@ -1700,7 +1694,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>582</v>
       </c>
@@ -1711,7 +1705,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="120" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>583</v>
       </c>
@@ -1722,7 +1716,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="150" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>584</v>
       </c>
@@ -1733,7 +1727,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="120" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" ht="116" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>585</v>
       </c>
@@ -1744,7 +1738,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>586</v>
       </c>
@@ -1755,7 +1749,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>587</v>
       </c>
@@ -1763,10 +1757,10 @@
         <v>73</v>
       </c>
       <c r="C72" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" ht="105" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="87" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>588</v>
       </c>
@@ -1777,7 +1771,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>589</v>
       </c>
@@ -1788,7 +1782,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>590</v>
       </c>
@@ -1799,7 +1793,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>591</v>
       </c>
@@ -1810,7 +1804,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>592</v>
       </c>
@@ -1821,7 +1815,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>593</v>
       </c>
@@ -1832,7 +1826,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>594</v>
       </c>
@@ -1843,7 +1837,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>595</v>
       </c>
@@ -1854,7 +1848,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="180" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>596</v>
       </c>
@@ -1865,7 +1859,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>597</v>
       </c>
@@ -1876,7 +1870,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="165" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" ht="145" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>598</v>
       </c>
@@ -1887,7 +1881,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="225" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>599</v>
       </c>
@@ -1898,7 +1892,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="150" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>600</v>
       </c>
@@ -1909,7 +1903,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>601</v>
       </c>
@@ -1920,7 +1914,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>602</v>
       </c>
@@ -1931,7 +1925,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="150" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>603</v>
       </c>
@@ -1942,7 +1936,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>604</v>
       </c>
@@ -1953,7 +1947,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>605</v>
       </c>
@@ -1964,7 +1958,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>606</v>
       </c>
@@ -1975,7 +1969,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>607</v>
       </c>
@@ -1986,7 +1980,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="180" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>608</v>
       </c>
@@ -1997,7 +1991,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>609</v>
       </c>
@@ -2008,7 +2002,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>610</v>
       </c>
@@ -2019,7 +2013,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="120" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" ht="116" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>611</v>
       </c>
@@ -2030,7 +2024,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>612</v>
       </c>
@@ -2041,7 +2035,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>613</v>
       </c>
@@ -2052,7 +2046,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>614</v>
       </c>
@@ -2063,7 +2057,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>615</v>
       </c>
@@ -2074,7 +2068,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>616</v>
       </c>
@@ -2085,7 +2079,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>617</v>
       </c>
@@ -2096,7 +2090,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="135" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" ht="116" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>618</v>
       </c>
@@ -2104,10 +2098,10 @@
         <v>104</v>
       </c>
       <c r="C103" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>619</v>
       </c>
@@ -2118,7 +2112,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>620</v>
       </c>
@@ -2126,10 +2120,10 @@
         <v>106</v>
       </c>
       <c r="C105" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>621</v>
       </c>
@@ -2137,10 +2131,10 @@
         <v>107</v>
       </c>
       <c r="C106" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>622</v>
       </c>
@@ -2151,7 +2145,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>623</v>
       </c>
@@ -2162,7 +2156,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="105" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" ht="87" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>624</v>
       </c>
@@ -2173,7 +2167,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="120" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" ht="116" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>625</v>
       </c>
@@ -2184,7 +2178,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>626</v>
       </c>
@@ -2195,7 +2189,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="135" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>627</v>
       </c>
@@ -2206,7 +2200,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>628</v>
       </c>
@@ -2217,7 +2211,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>629</v>
       </c>
@@ -2228,7 +2222,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>630</v>
       </c>
@@ -2239,7 +2233,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>631</v>
       </c>
@@ -2250,7 +2244,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>632</v>
       </c>
@@ -2261,7 +2255,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>633</v>
       </c>
@@ -2272,7 +2266,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="119" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>634</v>
       </c>
@@ -2283,7 +2277,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="120" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" ht="87" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>635</v>
       </c>
@@ -2294,7 +2288,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="121" spans="1:3" ht="165" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" ht="145" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>636</v>
       </c>
@@ -2305,7 +2299,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="122" spans="1:3" ht="135" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>637</v>
       </c>
@@ -2316,7 +2310,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>638</v>
       </c>
@@ -2327,7 +2321,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" ht="87" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>639</v>
       </c>
@@ -2338,7 +2332,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>640</v>
       </c>
@@ -2349,7 +2343,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="126" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>641</v>
       </c>
@@ -2360,7 +2354,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="127" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" ht="87" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>642</v>
       </c>
@@ -2371,7 +2365,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="105" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" ht="87" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>643</v>
       </c>
@@ -2379,10 +2373,10 @@
         <v>129</v>
       </c>
       <c r="C128" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>644</v>
       </c>
@@ -2393,7 +2387,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="130" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>645</v>
       </c>
@@ -2404,7 +2398,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="131" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>646</v>
       </c>
@@ -2415,7 +2409,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="132" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>647</v>
       </c>
@@ -2426,7 +2420,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>648</v>
       </c>
@@ -2437,7 +2431,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="134" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>649</v>
       </c>
@@ -2448,7 +2442,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="135" spans="1:3" ht="105" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>650</v>
       </c>
@@ -2456,10 +2450,10 @@
         <v>136</v>
       </c>
       <c r="C135" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" ht="120" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" ht="116" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>651</v>
       </c>
@@ -2470,7 +2464,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="137" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" ht="87" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>652</v>
       </c>
@@ -2481,7 +2475,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="138" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>653</v>
       </c>
@@ -2492,7 +2486,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="139" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>654</v>
       </c>
@@ -2503,7 +2497,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="140" spans="1:3" ht="165" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" ht="145" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>655</v>
       </c>
@@ -2514,7 +2508,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="141" spans="1:3" ht="165" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>656</v>
       </c>
@@ -2525,7 +2519,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="142" spans="1:3" ht="330" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>657</v>
       </c>
@@ -2536,7 +2530,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="143" spans="1:3" ht="120" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" ht="116" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>658</v>
       </c>
@@ -2547,7 +2541,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="144" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" ht="87" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>659</v>
       </c>
@@ -2555,10 +2549,10 @@
         <v>145</v>
       </c>
       <c r="C144" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>660</v>
       </c>
@@ -2569,7 +2563,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="146" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>661</v>
       </c>
@@ -2580,7 +2574,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="147" spans="1:3" ht="135" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>662</v>
       </c>
@@ -2591,7 +2585,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="148" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>663</v>
       </c>
@@ -2602,7 +2596,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="149" spans="1:3" ht="390" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" ht="348" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>664</v>
       </c>
@@ -2610,10 +2604,10 @@
         <v>150</v>
       </c>
       <c r="C149" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>665</v>
       </c>
@@ -2624,7 +2618,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>666</v>
       </c>
@@ -2635,7 +2629,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="152" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" ht="87" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>667</v>
       </c>
@@ -2646,7 +2640,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="153" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A153">
         <v>668</v>
       </c>
@@ -2657,7 +2651,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="154" spans="1:3" ht="255" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" ht="232" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>669</v>
       </c>
@@ -2668,7 +2662,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="155" spans="1:3" ht="90" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" ht="87" x14ac:dyDescent="0.35">
       <c r="A155">
         <v>670</v>
       </c>
@@ -2676,10 +2670,10 @@
         <v>156</v>
       </c>
       <c r="C155" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3" ht="135" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>671</v>
       </c>
@@ -2690,7 +2684,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="157" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A157">
         <v>672</v>
       </c>
@@ -2701,7 +2695,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="158" spans="1:3" ht="150" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" ht="145" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>673</v>
       </c>
@@ -2712,7 +2706,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="159" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>674</v>
       </c>
@@ -2723,7 +2717,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="160" spans="1:3" ht="255" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" ht="232" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>675</v>
       </c>
@@ -2734,7 +2728,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="161" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>676</v>
       </c>
@@ -2745,7 +2739,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="162" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>677</v>
       </c>
@@ -2756,7 +2750,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="163" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A163">
         <v>678</v>
       </c>
@@ -2767,7 +2761,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="164" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A164">
         <v>679</v>
       </c>
@@ -2778,7 +2772,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="165" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>680</v>
       </c>
@@ -2789,7 +2783,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="166" spans="1:3" ht="165" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" ht="145" x14ac:dyDescent="0.35">
       <c r="A166">
         <v>681</v>
       </c>
@@ -2797,10 +2791,10 @@
         <v>167</v>
       </c>
       <c r="C166" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A167">
         <v>682</v>
       </c>
@@ -2811,7 +2805,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>683</v>
       </c>
@@ -2822,7 +2816,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="169" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>684</v>
       </c>
@@ -2833,7 +2827,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="170" spans="1:3" ht="285" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" ht="261" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>685</v>
       </c>
@@ -2841,10 +2835,10 @@
         <v>171</v>
       </c>
       <c r="C170" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3" ht="135" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>686</v>
       </c>
@@ -2855,7 +2849,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A172">
         <v>687</v>
       </c>
@@ -2866,7 +2860,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A173">
         <v>688</v>
       </c>
@@ -2877,7 +2871,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="174" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A174">
         <v>689</v>
       </c>

--- a/annotated_data/mcmaster_reddit_part_3_A.xlsx
+++ b/annotated_data/mcmaster_reddit_part_3_A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mcmasteru365-my.sharepoint.com/personal/guz38_mcmaster_ca/Documents/COMPSCI 4NL3/cs4nl-final-project/annotated_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{D6F097C2-E5D3-46D9-8318-412C180C34CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C322D855-D0D9-4CCA-B52D-4C3E7EC7CBE8}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{D6F097C2-E5D3-46D9-8318-412C180C34CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{307EB380-8C7D-4944-974B-30E2A2B37C58}"/>
   <bookViews>
     <workbookView xWindow="4740" yWindow="3960" windowWidth="28800" windowHeight="15370" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="184">
   <si>
     <t>id</t>
   </si>
@@ -784,6 +784,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1561,6 +1565,9 @@
       <c r="B54" s="3" t="s">
         <v>55</v>
       </c>
+      <c r="C54" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row r="55" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A55">
